--- a/mumbai-real-estate/Mumbai_Real_Estate_Operating_System_v2.xlsx
+++ b/mumbai-real-estate/Mumbai_Real_Estate_Operating_System_v2.xlsx
@@ -1069,7 +1069,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>One corridor; 5 localities; 20–30 pockets named and mapped on verified boundaries</t>
+          <t>One corridor; 6 localities; 20–30 pockets named and mapped on verified boundaries</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>5 localities, 20–30 pockets locked; no expansion</t>
+          <t>6 localities, 20–30 pockets locked; no expansion</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
